--- a/Maths/Archive/Schlauch.xlsx
+++ b/Maths/Archive/Schlauch.xlsx
@@ -149,11 +149,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="259420234"/>
-        <c:axId val="376489454"/>
+        <c:axId val="444059318"/>
+        <c:axId val="413617827"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="259420234"/>
+        <c:axId val="444059318"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -205,10 +205,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="376489454"/>
+        <c:crossAx val="413617827"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="376489454"/>
+        <c:axId val="413617827"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -283,7 +283,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="259420234"/>
+        <c:crossAx val="444059318"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -370,11 +370,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="436132428"/>
-        <c:axId val="1481835736"/>
+        <c:axId val="441153554"/>
+        <c:axId val="745089181"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="436132428"/>
+        <c:axId val="441153554"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -426,10 +426,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1481835736"/>
+        <c:crossAx val="745089181"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1481835736"/>
+        <c:axId val="745089181"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -504,7 +504,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="436132428"/>
+        <c:crossAx val="441153554"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -591,11 +591,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="914514413"/>
-        <c:axId val="1342187871"/>
+        <c:axId val="47569495"/>
+        <c:axId val="1523534423"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="914514413"/>
+        <c:axId val="47569495"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -647,10 +647,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1342187871"/>
+        <c:crossAx val="1523534423"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1342187871"/>
+        <c:axId val="1523534423"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -725,7 +725,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="914514413"/>
+        <c:crossAx val="47569495"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -812,11 +812,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="417565260"/>
-        <c:axId val="62292699"/>
+        <c:axId val="1383538606"/>
+        <c:axId val="1485132953"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="417565260"/>
+        <c:axId val="1383538606"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -868,10 +868,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62292699"/>
+        <c:crossAx val="1485132953"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62292699"/>
+        <c:axId val="1485132953"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -946,7 +946,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417565260"/>
+        <c:crossAx val="1383538606"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
